--- a/data_voor_swing/aggregatietabellen/kern_kerntypering.xlsx
+++ b/data_voor_swing/aggregatietabellen/kern_kerntypering.xlsx
@@ -1,57 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4506"/>
-  <workbookPr showObjects="all" updateLinks="userSet" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" xWindow="480" yWindow="75" windowWidth="18075" windowHeight="12525" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="kern_kerntypering" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="125725" calcMode="auto" refMode="A1" iterateCount="100"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="17">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="166" formatCode="0.00"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
-    <numFmt numFmtId="168" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.00000"/>
-    <numFmt numFmtId="170" formatCode="0.000000"/>
-    <numFmt numFmtId="171" formatCode="0.0000000"/>
-    <numFmt numFmtId="172" formatCode="0.00000000"/>
-    <numFmt numFmtId="173" formatCode="0.000000000"/>
-    <numFmt numFmtId="174" formatCode="0.0000000000"/>
-    <numFmt numFmtId="175" formatCode="0.00000000000"/>
-    <numFmt numFmtId="176" formatCode="0.000000000000"/>
-    <numFmt numFmtId="177" formatCode="0.0000000000000"/>
-    <numFmt numFmtId="178" formatCode="0.00000000000000"/>
-    <numFmt numFmtId="179" formatCode="0.000000000000000"/>
-    <numFmt numFmtId="180" formatCode="0.0000000000000000"/>
-  </numFmts>
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -59,41 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -381,23 +420,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B296"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" s="0" outlineLevel="0">
-      <c r="A1" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>kern</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>kerntypering</t>
         </is>
       </c>
     </row>
-    <row r="2" spans="1:2" s="0" outlineLevel="0">
+    <row r="2">
       <c r="A2" t="inlineStr">
         <is>
           <t>71002_1</t>
@@ -409,7 +452,7 @@
         </is>
       </c>
     </row>
-    <row r="3" spans="1:2" s="0" outlineLevel="0">
+    <row r="3">
       <c r="A3" t="inlineStr">
         <is>
           <t>71002_2</t>
@@ -421,7 +464,7 @@
         </is>
       </c>
     </row>
-    <row r="4" spans="1:2" s="0" outlineLevel="0">
+    <row r="4">
       <c r="A4" t="inlineStr">
         <is>
           <t>71002_3</t>
@@ -433,7 +476,7 @@
         </is>
       </c>
     </row>
-    <row r="5" spans="1:2" s="0" outlineLevel="0">
+    <row r="5">
       <c r="A5" t="inlineStr">
         <is>
           <t>71002_4</t>
@@ -445,7 +488,7 @@
         </is>
       </c>
     </row>
-    <row r="6" spans="1:2" s="0" outlineLevel="0">
+    <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>71004_1</t>
@@ -457,7 +500,7 @@
         </is>
       </c>
     </row>
-    <row r="7" spans="1:2" s="0" outlineLevel="0">
+    <row r="7">
       <c r="A7" t="inlineStr">
         <is>
           <t>71004_2</t>
@@ -469,7 +512,7 @@
         </is>
       </c>
     </row>
-    <row r="8" spans="1:2" s="0" outlineLevel="0">
+    <row r="8">
       <c r="A8" t="inlineStr">
         <is>
           <t>71004_3</t>
@@ -481,7 +524,7 @@
         </is>
       </c>
     </row>
-    <row r="9" spans="1:2" s="0" outlineLevel="0">
+    <row r="9">
       <c r="A9" t="inlineStr">
         <is>
           <t>71004_4</t>
@@ -493,7 +536,7 @@
         </is>
       </c>
     </row>
-    <row r="10" spans="1:2" s="0" outlineLevel="0">
+    <row r="10">
       <c r="A10" t="inlineStr">
         <is>
           <t>71004_5</t>
@@ -505,7 +548,7 @@
         </is>
       </c>
     </row>
-    <row r="11" spans="1:2" s="0" outlineLevel="0">
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>71004_6</t>
@@ -517,7 +560,7 @@
         </is>
       </c>
     </row>
-    <row r="12" spans="1:2" s="0" outlineLevel="0">
+    <row r="12">
       <c r="A12" t="inlineStr">
         <is>
           <t>71004_7</t>
@@ -529,7 +572,7 @@
         </is>
       </c>
     </row>
-    <row r="13" spans="1:2" s="0" outlineLevel="0">
+    <row r="13">
       <c r="A13" t="inlineStr">
         <is>
           <t>71004_8</t>
@@ -541,7 +584,7 @@
         </is>
       </c>
     </row>
-    <row r="14" spans="1:2" s="0" outlineLevel="0">
+    <row r="14">
       <c r="A14" t="inlineStr">
         <is>
           <t>71011_1</t>
@@ -553,7 +596,7 @@
         </is>
       </c>
     </row>
-    <row r="15" spans="1:2" s="0" outlineLevel="0">
+    <row r="15">
       <c r="A15" t="inlineStr">
         <is>
           <t>71011_2</t>
@@ -565,7 +608,7 @@
         </is>
       </c>
     </row>
-    <row r="16" spans="1:2" s="0" outlineLevel="0">
+    <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>71011_3</t>
@@ -577,7 +620,7 @@
         </is>
       </c>
     </row>
-    <row r="17" spans="1:2" s="0" outlineLevel="0">
+    <row r="17">
       <c r="A17" t="inlineStr">
         <is>
           <t>71011_4</t>
@@ -589,7 +632,7 @@
         </is>
       </c>
     </row>
-    <row r="18" spans="1:2" s="0" outlineLevel="0">
+    <row r="18">
       <c r="A18" t="inlineStr">
         <is>
           <t>71011_5</t>
@@ -601,7 +644,7 @@
         </is>
       </c>
     </row>
-    <row r="19" spans="1:2" s="0" outlineLevel="0">
+    <row r="19">
       <c r="A19" t="inlineStr">
         <is>
           <t>71011_6</t>
@@ -613,7 +656,7 @@
         </is>
       </c>
     </row>
-    <row r="20" spans="1:2" s="0" outlineLevel="0">
+    <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>71016_1</t>
@@ -625,7 +668,7 @@
         </is>
       </c>
     </row>
-    <row r="21" spans="1:2" s="0" outlineLevel="0">
+    <row r="21">
       <c r="A21" t="inlineStr">
         <is>
           <t>71016_10</t>
@@ -637,7 +680,7 @@
         </is>
       </c>
     </row>
-    <row r="22" spans="1:2" s="0" outlineLevel="0">
+    <row r="22">
       <c r="A22" t="inlineStr">
         <is>
           <t>71016_11</t>
@@ -649,7 +692,7 @@
         </is>
       </c>
     </row>
-    <row r="23" spans="1:2" s="0" outlineLevel="0">
+    <row r="23">
       <c r="A23" t="inlineStr">
         <is>
           <t>71016_12</t>
@@ -661,7 +704,7 @@
         </is>
       </c>
     </row>
-    <row r="24" spans="1:2" s="0" outlineLevel="0">
+    <row r="24">
       <c r="A24" t="inlineStr">
         <is>
           <t>71016_13</t>
@@ -673,7 +716,7 @@
         </is>
       </c>
     </row>
-    <row r="25" spans="1:2" s="0" outlineLevel="0">
+    <row r="25">
       <c r="A25" t="inlineStr">
         <is>
           <t>71016_14</t>
@@ -685,7 +728,7 @@
         </is>
       </c>
     </row>
-    <row r="26" spans="1:2" s="0" outlineLevel="0">
+    <row r="26">
       <c r="A26" t="inlineStr">
         <is>
           <t>71016_2</t>
@@ -697,7 +740,7 @@
         </is>
       </c>
     </row>
-    <row r="27" spans="1:2" s="0" outlineLevel="0">
+    <row r="27">
       <c r="A27" t="inlineStr">
         <is>
           <t>71016_3</t>
@@ -709,7 +752,7 @@
         </is>
       </c>
     </row>
-    <row r="28" spans="1:2" s="0" outlineLevel="0">
+    <row r="28">
       <c r="A28" t="inlineStr">
         <is>
           <t>71016_4</t>
@@ -721,7 +764,7 @@
         </is>
       </c>
     </row>
-    <row r="29" spans="1:2" s="0" outlineLevel="0">
+    <row r="29">
       <c r="A29" t="inlineStr">
         <is>
           <t>71016_5</t>
@@ -733,7 +776,7 @@
         </is>
       </c>
     </row>
-    <row r="30" spans="1:2" s="0" outlineLevel="0">
+    <row r="30">
       <c r="A30" t="inlineStr">
         <is>
           <t>71016_6</t>
@@ -745,7 +788,7 @@
         </is>
       </c>
     </row>
-    <row r="31" spans="1:2" s="0" outlineLevel="0">
+    <row r="31">
       <c r="A31" t="inlineStr">
         <is>
           <t>71016_7</t>
@@ -757,7 +800,7 @@
         </is>
       </c>
     </row>
-    <row r="32" spans="1:2" s="0" outlineLevel="0">
+    <row r="32">
       <c r="A32" t="inlineStr">
         <is>
           <t>71016_8</t>
@@ -769,7 +812,7 @@
         </is>
       </c>
     </row>
-    <row r="33" spans="1:2" s="0" outlineLevel="0">
+    <row r="33">
       <c r="A33" t="inlineStr">
         <is>
           <t>71016_9</t>
@@ -781,7 +824,7 @@
         </is>
       </c>
     </row>
-    <row r="34" spans="1:2" s="0" outlineLevel="0">
+    <row r="34">
       <c r="A34" t="inlineStr">
         <is>
           <t>71017_1</t>
@@ -793,7 +836,7 @@
         </is>
       </c>
     </row>
-    <row r="35" spans="1:2" s="0" outlineLevel="0">
+    <row r="35">
       <c r="A35" t="inlineStr">
         <is>
           <t>71017_2</t>
@@ -805,7 +848,7 @@
         </is>
       </c>
     </row>
-    <row r="36" spans="1:2" s="0" outlineLevel="0">
+    <row r="36">
       <c r="A36" t="inlineStr">
         <is>
           <t>71017_3</t>
@@ -817,7 +860,7 @@
         </is>
       </c>
     </row>
-    <row r="37" spans="1:2" s="0" outlineLevel="0">
+    <row r="37">
       <c r="A37" t="inlineStr">
         <is>
           <t>71017_4</t>
@@ -829,7 +872,7 @@
         </is>
       </c>
     </row>
-    <row r="38" spans="1:2" s="0" outlineLevel="0">
+    <row r="38">
       <c r="A38" t="inlineStr">
         <is>
           <t>71017_5</t>
@@ -841,7 +884,7 @@
         </is>
       </c>
     </row>
-    <row r="39" spans="1:2" s="0" outlineLevel="0">
+    <row r="39">
       <c r="A39" t="inlineStr">
         <is>
           <t>71017_6</t>
@@ -853,7 +896,7 @@
         </is>
       </c>
     </row>
-    <row r="40" spans="1:2" s="0" outlineLevel="0">
+    <row r="40">
       <c r="A40" t="inlineStr">
         <is>
           <t>71017_7</t>
@@ -865,7 +908,7 @@
         </is>
       </c>
     </row>
-    <row r="41" spans="1:2" s="0" outlineLevel="0">
+    <row r="41">
       <c r="A41" t="inlineStr">
         <is>
           <t>71020_1</t>
@@ -877,7 +920,7 @@
         </is>
       </c>
     </row>
-    <row r="42" spans="1:2" s="0" outlineLevel="0">
+    <row r="42">
       <c r="A42" t="inlineStr">
         <is>
           <t>71020_2</t>
@@ -889,7 +932,7 @@
         </is>
       </c>
     </row>
-    <row r="43" spans="1:2" s="0" outlineLevel="0">
+    <row r="43">
       <c r="A43" t="inlineStr">
         <is>
           <t>71020_3</t>
@@ -901,7 +944,7 @@
         </is>
       </c>
     </row>
-    <row r="44" spans="1:2" s="0" outlineLevel="0">
+    <row r="44">
       <c r="A44" t="inlineStr">
         <is>
           <t>71022_1</t>
@@ -913,7 +956,7 @@
         </is>
       </c>
     </row>
-    <row r="45" spans="1:2" s="0" outlineLevel="0">
+    <row r="45">
       <c r="A45" t="inlineStr">
         <is>
           <t>71022_10</t>
@@ -925,7 +968,7 @@
         </is>
       </c>
     </row>
-    <row r="46" spans="1:2" s="0" outlineLevel="0">
+    <row r="46">
       <c r="A46" t="inlineStr">
         <is>
           <t>71022_11</t>
@@ -937,7 +980,7 @@
         </is>
       </c>
     </row>
-    <row r="47" spans="1:2" s="0" outlineLevel="0">
+    <row r="47">
       <c r="A47" t="inlineStr">
         <is>
           <t>71022_12</t>
@@ -949,7 +992,7 @@
         </is>
       </c>
     </row>
-    <row r="48" spans="1:2" s="0" outlineLevel="0">
+    <row r="48">
       <c r="A48" t="inlineStr">
         <is>
           <t>71022_13</t>
@@ -961,7 +1004,7 @@
         </is>
       </c>
     </row>
-    <row r="49" spans="1:2" s="0" outlineLevel="0">
+    <row r="49">
       <c r="A49" t="inlineStr">
         <is>
           <t>71022_2</t>
@@ -973,7 +1016,7 @@
         </is>
       </c>
     </row>
-    <row r="50" spans="1:2" s="0" outlineLevel="0">
+    <row r="50">
       <c r="A50" t="inlineStr">
         <is>
           <t>71022_3</t>
@@ -985,7 +1028,7 @@
         </is>
       </c>
     </row>
-    <row r="51" spans="1:2" s="0" outlineLevel="0">
+    <row r="51">
       <c r="A51" t="inlineStr">
         <is>
           <t>71022_4</t>
@@ -997,7 +1040,7 @@
         </is>
       </c>
     </row>
-    <row r="52" spans="1:2" s="0" outlineLevel="0">
+    <row r="52">
       <c r="A52" t="inlineStr">
         <is>
           <t>71022_5</t>
@@ -1009,7 +1052,7 @@
         </is>
       </c>
     </row>
-    <row r="53" spans="1:2" s="0" outlineLevel="0">
+    <row r="53">
       <c r="A53" t="inlineStr">
         <is>
           <t>71022_6</t>
@@ -1021,7 +1064,7 @@
         </is>
       </c>
     </row>
-    <row r="54" spans="1:2" s="0" outlineLevel="0">
+    <row r="54">
       <c r="A54" t="inlineStr">
         <is>
           <t>71022_7</t>
@@ -1033,7 +1076,7 @@
         </is>
       </c>
     </row>
-    <row r="55" spans="1:2" s="0" outlineLevel="0">
+    <row r="55">
       <c r="A55" t="inlineStr">
         <is>
           <t>71022_8</t>
@@ -1045,7 +1088,7 @@
         </is>
       </c>
     </row>
-    <row r="56" spans="1:2" s="0" outlineLevel="0">
+    <row r="56">
       <c r="A56" t="inlineStr">
         <is>
           <t>71022_9</t>
@@ -1057,7 +1100,7 @@
         </is>
       </c>
     </row>
-    <row r="57" spans="1:2" s="0" outlineLevel="0">
+    <row r="57">
       <c r="A57" t="inlineStr">
         <is>
           <t>71024_1</t>
@@ -1069,7 +1112,7 @@
         </is>
       </c>
     </row>
-    <row r="58" spans="1:2" s="0" outlineLevel="0">
+    <row r="58">
       <c r="A58" t="inlineStr">
         <is>
           <t>71024_2</t>
@@ -1081,7 +1124,7 @@
         </is>
       </c>
     </row>
-    <row r="59" spans="1:2" s="0" outlineLevel="0">
+    <row r="59">
       <c r="A59" t="inlineStr">
         <is>
           <t>71024_3</t>
@@ -1093,7 +1136,7 @@
         </is>
       </c>
     </row>
-    <row r="60" spans="1:2" s="0" outlineLevel="0">
+    <row r="60">
       <c r="A60" t="inlineStr">
         <is>
           <t>71024_4</t>
@@ -1105,7 +1148,7 @@
         </is>
       </c>
     </row>
-    <row r="61" spans="1:2" s="0" outlineLevel="0">
+    <row r="61">
       <c r="A61" t="inlineStr">
         <is>
           <t>71024_5</t>
@@ -1117,7 +1160,7 @@
         </is>
       </c>
     </row>
-    <row r="62" spans="1:2" s="0" outlineLevel="0">
+    <row r="62">
       <c r="A62" t="inlineStr">
         <is>
           <t>71034_2</t>
@@ -1129,7 +1172,7 @@
         </is>
       </c>
     </row>
-    <row r="63" spans="1:2" s="0" outlineLevel="0">
+    <row r="63">
       <c r="A63" t="inlineStr">
         <is>
           <t>71034_3</t>
@@ -1141,7 +1184,7 @@
         </is>
       </c>
     </row>
-    <row r="64" spans="1:2" s="0" outlineLevel="0">
+    <row r="64">
       <c r="A64" t="inlineStr">
         <is>
           <t>71034_4</t>
@@ -1153,7 +1196,7 @@
         </is>
       </c>
     </row>
-    <row r="65" spans="1:2" s="0" outlineLevel="0">
+    <row r="65">
       <c r="A65" t="inlineStr">
         <is>
           <t>71037_1</t>
@@ -1165,7 +1208,7 @@
         </is>
       </c>
     </row>
-    <row r="66" spans="1:2" s="0" outlineLevel="0">
+    <row r="66">
       <c r="A66" t="inlineStr">
         <is>
           <t>71037_2</t>
@@ -1177,7 +1220,7 @@
         </is>
       </c>
     </row>
-    <row r="67" spans="1:2" s="0" outlineLevel="0">
+    <row r="67">
       <c r="A67" t="inlineStr">
         <is>
           <t>71037_3</t>
@@ -1189,7 +1232,7 @@
         </is>
       </c>
     </row>
-    <row r="68" spans="1:2" s="0" outlineLevel="0">
+    <row r="68">
       <c r="A68" t="inlineStr">
         <is>
           <t>71037_4</t>
@@ -1201,7 +1244,7 @@
         </is>
       </c>
     </row>
-    <row r="69" spans="1:2" s="0" outlineLevel="0">
+    <row r="69">
       <c r="A69" t="inlineStr">
         <is>
           <t>71037_5</t>
@@ -1213,7 +1256,7 @@
         </is>
       </c>
     </row>
-    <row r="70" spans="1:2" s="0" outlineLevel="0">
+    <row r="70">
       <c r="A70" t="inlineStr">
         <is>
           <t>71037_6</t>
@@ -1225,7 +1268,7 @@
         </is>
       </c>
     </row>
-    <row r="71" spans="1:2" s="0" outlineLevel="0">
+    <row r="71">
       <c r="A71" t="inlineStr">
         <is>
           <t>71045_1</t>
@@ -1237,7 +1280,7 @@
         </is>
       </c>
     </row>
-    <row r="72" spans="1:2" s="0" outlineLevel="0">
+    <row r="72">
       <c r="A72" t="inlineStr">
         <is>
           <t>71045_2</t>
@@ -1249,7 +1292,7 @@
         </is>
       </c>
     </row>
-    <row r="73" spans="1:2" s="0" outlineLevel="0">
+    <row r="73">
       <c r="A73" t="inlineStr">
         <is>
           <t>71045_3</t>
@@ -1261,7 +1304,7 @@
         </is>
       </c>
     </row>
-    <row r="74" spans="1:2" s="0" outlineLevel="0">
+    <row r="74">
       <c r="A74" t="inlineStr">
         <is>
           <t>71045_4</t>
@@ -1273,7 +1316,7 @@
         </is>
       </c>
     </row>
-    <row r="75" spans="1:2" s="0" outlineLevel="0">
+    <row r="75">
       <c r="A75" t="inlineStr">
         <is>
           <t>71053_1</t>
@@ -1285,7 +1328,7 @@
         </is>
       </c>
     </row>
-    <row r="76" spans="1:2" s="0" outlineLevel="0">
+    <row r="76">
       <c r="A76" t="inlineStr">
         <is>
           <t>71053_10</t>
@@ -1297,7 +1340,7 @@
         </is>
       </c>
     </row>
-    <row r="77" spans="1:2" s="0" outlineLevel="0">
+    <row r="77">
       <c r="A77" t="inlineStr">
         <is>
           <t>71053_11</t>
@@ -1309,7 +1352,7 @@
         </is>
       </c>
     </row>
-    <row r="78" spans="1:2" s="0" outlineLevel="0">
+    <row r="78">
       <c r="A78" t="inlineStr">
         <is>
           <t>71053_12</t>
@@ -1321,7 +1364,7 @@
         </is>
       </c>
     </row>
-    <row r="79" spans="1:2" s="0" outlineLevel="0">
+    <row r="79">
       <c r="A79" t="inlineStr">
         <is>
           <t>71053_13</t>
@@ -1333,7 +1376,7 @@
         </is>
       </c>
     </row>
-    <row r="80" spans="1:2" s="0" outlineLevel="0">
+    <row r="80">
       <c r="A80" t="inlineStr">
         <is>
           <t>71053_14</t>
@@ -1345,7 +1388,7 @@
         </is>
       </c>
     </row>
-    <row r="81" spans="1:2" s="0" outlineLevel="0">
+    <row r="81">
       <c r="A81" t="inlineStr">
         <is>
           <t>71053_15</t>
@@ -1357,7 +1400,7 @@
         </is>
       </c>
     </row>
-    <row r="82" spans="1:2" s="0" outlineLevel="0">
+    <row r="82">
       <c r="A82" t="inlineStr">
         <is>
           <t>71053_16</t>
@@ -1369,7 +1412,7 @@
         </is>
       </c>
     </row>
-    <row r="83" spans="1:2" s="0" outlineLevel="0">
+    <row r="83">
       <c r="A83" t="inlineStr">
         <is>
           <t>71053_17</t>
@@ -1381,7 +1424,7 @@
         </is>
       </c>
     </row>
-    <row r="84" spans="1:2" s="0" outlineLevel="0">
+    <row r="84">
       <c r="A84" t="inlineStr">
         <is>
           <t>71053_18</t>
@@ -1393,7 +1436,7 @@
         </is>
       </c>
     </row>
-    <row r="85" spans="1:2" s="0" outlineLevel="0">
+    <row r="85">
       <c r="A85" t="inlineStr">
         <is>
           <t>71053_2</t>
@@ -1405,7 +1448,7 @@
         </is>
       </c>
     </row>
-    <row r="86" spans="1:2" s="0" outlineLevel="0">
+    <row r="86">
       <c r="A86" t="inlineStr">
         <is>
           <t>71053_3</t>
@@ -1417,7 +1460,7 @@
         </is>
       </c>
     </row>
-    <row r="87" spans="1:2" s="0" outlineLevel="0">
+    <row r="87">
       <c r="A87" t="inlineStr">
         <is>
           <t>71053_4</t>
@@ -1429,7 +1472,7 @@
         </is>
       </c>
     </row>
-    <row r="88" spans="1:2" s="0" outlineLevel="0">
+    <row r="88">
       <c r="A88" t="inlineStr">
         <is>
           <t>71053_5</t>
@@ -1441,7 +1484,7 @@
         </is>
       </c>
     </row>
-    <row r="89" spans="1:2" s="0" outlineLevel="0">
+    <row r="89">
       <c r="A89" t="inlineStr">
         <is>
           <t>71053_6</t>
@@ -1453,7 +1496,7 @@
         </is>
       </c>
     </row>
-    <row r="90" spans="1:2" s="0" outlineLevel="0">
+    <row r="90">
       <c r="A90" t="inlineStr">
         <is>
           <t>71053_7</t>
@@ -1465,7 +1508,7 @@
         </is>
       </c>
     </row>
-    <row r="91" spans="1:2" s="0" outlineLevel="0">
+    <row r="91">
       <c r="A91" t="inlineStr">
         <is>
           <t>71053_8</t>
@@ -1477,7 +1520,7 @@
         </is>
       </c>
     </row>
-    <row r="92" spans="1:2" s="0" outlineLevel="0">
+    <row r="92">
       <c r="A92" t="inlineStr">
         <is>
           <t>71053_9</t>
@@ -1489,7 +1532,7 @@
         </is>
       </c>
     </row>
-    <row r="93" spans="1:2" s="0" outlineLevel="0">
+    <row r="93">
       <c r="A93" t="inlineStr">
         <is>
           <t>71057_1</t>
@@ -1501,7 +1544,7 @@
         </is>
       </c>
     </row>
-    <row r="94" spans="1:2" s="0" outlineLevel="0">
+    <row r="94">
       <c r="A94" t="inlineStr">
         <is>
           <t>71057_2</t>
@@ -1513,7 +1556,7 @@
         </is>
       </c>
     </row>
-    <row r="95" spans="1:2" s="0" outlineLevel="0">
+    <row r="95">
       <c r="A95" t="inlineStr">
         <is>
           <t>71057_3</t>
@@ -1525,7 +1568,7 @@
         </is>
       </c>
     </row>
-    <row r="96" spans="1:2" s="0" outlineLevel="0">
+    <row r="96">
       <c r="A96" t="inlineStr">
         <is>
           <t>71057_4</t>
@@ -1537,7 +1580,7 @@
         </is>
       </c>
     </row>
-    <row r="97" spans="1:2" s="0" outlineLevel="0">
+    <row r="97">
       <c r="A97" t="inlineStr">
         <is>
           <t>71066_1</t>
@@ -1549,7 +1592,7 @@
         </is>
       </c>
     </row>
-    <row r="98" spans="1:2" s="0" outlineLevel="0">
+    <row r="98">
       <c r="A98" t="inlineStr">
         <is>
           <t>71066_2</t>
@@ -1561,7 +1604,7 @@
         </is>
       </c>
     </row>
-    <row r="99" spans="1:2" s="0" outlineLevel="0">
+    <row r="99">
       <c r="A99" t="inlineStr">
         <is>
           <t>71066_3</t>
@@ -1573,7 +1616,7 @@
         </is>
       </c>
     </row>
-    <row r="100" spans="1:2" s="0" outlineLevel="0">
+    <row r="100">
       <c r="A100" t="inlineStr">
         <is>
           <t>71066_4</t>
@@ -1585,7 +1628,7 @@
         </is>
       </c>
     </row>
-    <row r="101" spans="1:2" s="0" outlineLevel="0">
+    <row r="101">
       <c r="A101" t="inlineStr">
         <is>
           <t>71067_1</t>
@@ -1597,7 +1640,7 @@
         </is>
       </c>
     </row>
-    <row r="102" spans="1:2" s="0" outlineLevel="0">
+    <row r="102">
       <c r="A102" t="inlineStr">
         <is>
           <t>71067_2</t>
@@ -1609,7 +1652,7 @@
         </is>
       </c>
     </row>
-    <row r="103" spans="1:2" s="0" outlineLevel="0">
+    <row r="103">
       <c r="A103" t="inlineStr">
         <is>
           <t>71067_3</t>
@@ -1621,7 +1664,7 @@
         </is>
       </c>
     </row>
-    <row r="104" spans="1:2" s="0" outlineLevel="0">
+    <row r="104">
       <c r="A104" t="inlineStr">
         <is>
           <t>71067_4</t>
@@ -1633,7 +1676,7 @@
         </is>
       </c>
     </row>
-    <row r="105" spans="1:2" s="0" outlineLevel="0">
+    <row r="105">
       <c r="A105" t="inlineStr">
         <is>
           <t>71069_1</t>
@@ -1645,7 +1688,7 @@
         </is>
       </c>
     </row>
-    <row r="106" spans="1:2" s="0" outlineLevel="0">
+    <row r="106">
       <c r="A106" t="inlineStr">
         <is>
           <t>71069_2</t>
@@ -1657,7 +1700,7 @@
         </is>
       </c>
     </row>
-    <row r="107" spans="1:2" s="0" outlineLevel="0">
+    <row r="107">
       <c r="A107" t="inlineStr">
         <is>
           <t>71069_3</t>
@@ -1669,7 +1712,7 @@
         </is>
       </c>
     </row>
-    <row r="108" spans="1:2" s="0" outlineLevel="0">
+    <row r="108">
       <c r="A108" t="inlineStr">
         <is>
           <t>71070_1</t>
@@ -1681,7 +1724,7 @@
         </is>
       </c>
     </row>
-    <row r="109" spans="1:2" s="0" outlineLevel="0">
+    <row r="109">
       <c r="A109" t="inlineStr">
         <is>
           <t>71070_2</t>
@@ -1693,7 +1736,7 @@
         </is>
       </c>
     </row>
-    <row r="110" spans="1:2" s="0" outlineLevel="0">
+    <row r="110">
       <c r="A110" t="inlineStr">
         <is>
           <t>71070_3</t>
@@ -1705,7 +1748,7 @@
         </is>
       </c>
     </row>
-    <row r="111" spans="1:2" s="0" outlineLevel="0">
+    <row r="111">
       <c r="A111" t="inlineStr">
         <is>
           <t>71070_4</t>
@@ -1717,7 +1760,7 @@
         </is>
       </c>
     </row>
-    <row r="112" spans="1:2" s="0" outlineLevel="0">
+    <row r="112">
       <c r="A112" t="inlineStr">
         <is>
           <t>71070_5</t>
@@ -1729,7 +1772,7 @@
         </is>
       </c>
     </row>
-    <row r="113" spans="1:2" s="0" outlineLevel="0">
+    <row r="113">
       <c r="A113" t="inlineStr">
         <is>
           <t>71070_6</t>
@@ -1741,7 +1784,7 @@
         </is>
       </c>
     </row>
-    <row r="114" spans="1:2" s="0" outlineLevel="0">
+    <row r="114">
       <c r="A114" t="inlineStr">
         <is>
           <t>71070_7</t>
@@ -1753,7 +1796,7 @@
         </is>
       </c>
     </row>
-    <row r="115" spans="1:2" s="0" outlineLevel="0">
+    <row r="115">
       <c r="A115" t="inlineStr">
         <is>
           <t>71070_8</t>
@@ -1765,7 +1808,7 @@
         </is>
       </c>
     </row>
-    <row r="116" spans="1:2" s="0" outlineLevel="0">
+    <row r="116">
       <c r="A116" t="inlineStr">
         <is>
           <t>71070_9</t>
@@ -1777,7 +1820,7 @@
         </is>
       </c>
     </row>
-    <row r="117" spans="1:2" s="0" outlineLevel="0">
+    <row r="117">
       <c r="A117" t="inlineStr">
         <is>
           <t>72003_1</t>
@@ -1789,7 +1832,7 @@
         </is>
       </c>
     </row>
-    <row r="118" spans="1:2" s="0" outlineLevel="0">
+    <row r="118">
       <c r="A118" t="inlineStr">
         <is>
           <t>72003_2</t>
@@ -1801,7 +1844,7 @@
         </is>
       </c>
     </row>
-    <row r="119" spans="1:2" s="0" outlineLevel="0">
+    <row r="119">
       <c r="A119" t="inlineStr">
         <is>
           <t>72003_3</t>
@@ -1813,7 +1856,7 @@
         </is>
       </c>
     </row>
-    <row r="120" spans="1:2" s="0" outlineLevel="0">
+    <row r="120">
       <c r="A120" t="inlineStr">
         <is>
           <t>72003_4</t>
@@ -1825,7 +1868,7 @@
         </is>
       </c>
     </row>
-    <row r="121" spans="1:2" s="0" outlineLevel="0">
+    <row r="121">
       <c r="A121" t="inlineStr">
         <is>
           <t>72003_5</t>
@@ -1837,7 +1880,7 @@
         </is>
       </c>
     </row>
-    <row r="122" spans="1:2" s="0" outlineLevel="0">
+    <row r="122">
       <c r="A122" t="inlineStr">
         <is>
           <t>72004_1</t>
@@ -1849,7 +1892,7 @@
         </is>
       </c>
     </row>
-    <row r="123" spans="1:2" s="0" outlineLevel="0">
+    <row r="123">
       <c r="A123" t="inlineStr">
         <is>
           <t>72004_2</t>
@@ -1861,7 +1904,7 @@
         </is>
       </c>
     </row>
-    <row r="124" spans="1:2" s="0" outlineLevel="0">
+    <row r="124">
       <c r="A124" t="inlineStr">
         <is>
           <t>72004_3</t>
@@ -1873,7 +1916,7 @@
         </is>
       </c>
     </row>
-    <row r="125" spans="1:2" s="0" outlineLevel="0">
+    <row r="125">
       <c r="A125" t="inlineStr">
         <is>
           <t>72004_4</t>
@@ -1885,7 +1928,7 @@
         </is>
       </c>
     </row>
-    <row r="126" spans="1:2" s="0" outlineLevel="0">
+    <row r="126">
       <c r="A126" t="inlineStr">
         <is>
           <t>72004_5</t>
@@ -1897,7 +1940,7 @@
         </is>
       </c>
     </row>
-    <row r="127" spans="1:2" s="0" outlineLevel="0">
+    <row r="127">
       <c r="A127" t="inlineStr">
         <is>
           <t>72018_1</t>
@@ -1909,7 +1952,7 @@
         </is>
       </c>
     </row>
-    <row r="128" spans="1:2" s="0" outlineLevel="0">
+    <row r="128">
       <c r="A128" t="inlineStr">
         <is>
           <t>72018_2</t>
@@ -1921,7 +1964,7 @@
         </is>
       </c>
     </row>
-    <row r="129" spans="1:2" s="0" outlineLevel="0">
+    <row r="129">
       <c r="A129" t="inlineStr">
         <is>
           <t>72018_3</t>
@@ -1933,7 +1976,7 @@
         </is>
       </c>
     </row>
-    <row r="130" spans="1:2" s="0" outlineLevel="0">
+    <row r="130">
       <c r="A130" t="inlineStr">
         <is>
           <t>72018_4</t>
@@ -1945,7 +1988,7 @@
         </is>
       </c>
     </row>
-    <row r="131" spans="1:2" s="0" outlineLevel="0">
+    <row r="131">
       <c r="A131" t="inlineStr">
         <is>
           <t>72018_5</t>
@@ -1957,7 +2000,7 @@
         </is>
       </c>
     </row>
-    <row r="132" spans="1:2" s="0" outlineLevel="0">
+    <row r="132">
       <c r="A132" t="inlineStr">
         <is>
           <t>72020_1</t>
@@ -1969,7 +2012,7 @@
         </is>
       </c>
     </row>
-    <row r="133" spans="1:2" s="0" outlineLevel="0">
+    <row r="133">
       <c r="A133" t="inlineStr">
         <is>
           <t>72020_10</t>
@@ -1981,7 +2024,7 @@
         </is>
       </c>
     </row>
-    <row r="134" spans="1:2" s="0" outlineLevel="0">
+    <row r="134">
       <c r="A134" t="inlineStr">
         <is>
           <t>72020_2</t>
@@ -1993,7 +2036,7 @@
         </is>
       </c>
     </row>
-    <row r="135" spans="1:2" s="0" outlineLevel="0">
+    <row r="135">
       <c r="A135" t="inlineStr">
         <is>
           <t>72020_3</t>
@@ -2005,7 +2048,7 @@
         </is>
       </c>
     </row>
-    <row r="136" spans="1:2" s="0" outlineLevel="0">
+    <row r="136">
       <c r="A136" t="inlineStr">
         <is>
           <t>72020_4</t>
@@ -2017,7 +2060,7 @@
         </is>
       </c>
     </row>
-    <row r="137" spans="1:2" s="0" outlineLevel="0">
+    <row r="137">
       <c r="A137" t="inlineStr">
         <is>
           <t>72020_5</t>
@@ -2029,7 +2072,7 @@
         </is>
       </c>
     </row>
-    <row r="138" spans="1:2" s="0" outlineLevel="0">
+    <row r="138">
       <c r="A138" t="inlineStr">
         <is>
           <t>72020_6</t>
@@ -2041,7 +2084,7 @@
         </is>
       </c>
     </row>
-    <row r="139" spans="1:2" s="0" outlineLevel="0">
+    <row r="139">
       <c r="A139" t="inlineStr">
         <is>
           <t>72020_7</t>
@@ -2053,7 +2096,7 @@
         </is>
       </c>
     </row>
-    <row r="140" spans="1:2" s="0" outlineLevel="0">
+    <row r="140">
       <c r="A140" t="inlineStr">
         <is>
           <t>72020_8</t>
@@ -2065,7 +2108,7 @@
         </is>
       </c>
     </row>
-    <row r="141" spans="1:2" s="0" outlineLevel="0">
+    <row r="141">
       <c r="A141" t="inlineStr">
         <is>
           <t>72020_9</t>
@@ -2077,7 +2120,7 @@
         </is>
       </c>
     </row>
-    <row r="142" spans="1:2" s="0" outlineLevel="0">
+    <row r="142">
       <c r="A142" t="inlineStr">
         <is>
           <t>72021_1</t>
@@ -2089,7 +2132,7 @@
         </is>
       </c>
     </row>
-    <row r="143" spans="1:2" s="0" outlineLevel="0">
+    <row r="143">
       <c r="A143" t="inlineStr">
         <is>
           <t>72021_2</t>
@@ -2101,7 +2144,7 @@
         </is>
       </c>
     </row>
-    <row r="144" spans="1:2" s="0" outlineLevel="0">
+    <row r="144">
       <c r="A144" t="inlineStr">
         <is>
           <t>72021_3</t>
@@ -2113,7 +2156,7 @@
         </is>
       </c>
     </row>
-    <row r="145" spans="1:2" s="0" outlineLevel="0">
+    <row r="145">
       <c r="A145" t="inlineStr">
         <is>
           <t>72021_4</t>
@@ -2125,7 +2168,7 @@
         </is>
       </c>
     </row>
-    <row r="146" spans="1:2" s="0" outlineLevel="0">
+    <row r="146">
       <c r="A146" t="inlineStr">
         <is>
           <t>72021_5</t>
@@ -2137,7 +2180,7 @@
         </is>
       </c>
     </row>
-    <row r="147" spans="1:2" s="0" outlineLevel="0">
+    <row r="147">
       <c r="A147" t="inlineStr">
         <is>
           <t>72021_6</t>
@@ -2149,7 +2192,7 @@
         </is>
       </c>
     </row>
-    <row r="148" spans="1:2" s="0" outlineLevel="0">
+    <row r="148">
       <c r="A148" t="inlineStr">
         <is>
           <t>72021_7</t>
@@ -2161,7 +2204,7 @@
         </is>
       </c>
     </row>
-    <row r="149" spans="1:2" s="0" outlineLevel="0">
+    <row r="149">
       <c r="A149" t="inlineStr">
         <is>
           <t>72030_1</t>
@@ -2173,7 +2216,7 @@
         </is>
       </c>
     </row>
-    <row r="150" spans="1:2" s="0" outlineLevel="0">
+    <row r="150">
       <c r="A150" t="inlineStr">
         <is>
           <t>72030_2</t>
@@ -2185,7 +2228,7 @@
         </is>
       </c>
     </row>
-    <row r="151" spans="1:2" s="0" outlineLevel="0">
+    <row r="151">
       <c r="A151" t="inlineStr">
         <is>
           <t>72030_3</t>
@@ -2197,7 +2240,7 @@
         </is>
       </c>
     </row>
-    <row r="152" spans="1:2" s="0" outlineLevel="0">
+    <row r="152">
       <c r="A152" t="inlineStr">
         <is>
           <t>72030_4</t>
@@ -2209,7 +2252,7 @@
         </is>
       </c>
     </row>
-    <row r="153" spans="1:2" s="0" outlineLevel="0">
+    <row r="153">
       <c r="A153" t="inlineStr">
         <is>
           <t>72030_5</t>
@@ -2221,7 +2264,7 @@
         </is>
       </c>
     </row>
-    <row r="154" spans="1:2" s="0" outlineLevel="0">
+    <row r="154">
       <c r="A154" t="inlineStr">
         <is>
           <t>72030_6</t>
@@ -2233,7 +2276,7 @@
         </is>
       </c>
     </row>
-    <row r="155" spans="1:2" s="0" outlineLevel="0">
+    <row r="155">
       <c r="A155" t="inlineStr">
         <is>
           <t>72037_1</t>
@@ -2245,7 +2288,7 @@
         </is>
       </c>
     </row>
-    <row r="156" spans="1:2" s="0" outlineLevel="0">
+    <row r="156">
       <c r="A156" t="inlineStr">
         <is>
           <t>72037_2</t>
@@ -2257,7 +2300,7 @@
         </is>
       </c>
     </row>
-    <row r="157" spans="1:2" s="0" outlineLevel="0">
+    <row r="157">
       <c r="A157" t="inlineStr">
         <is>
           <t>72037_3</t>
@@ -2269,7 +2312,7 @@
         </is>
       </c>
     </row>
-    <row r="158" spans="1:2" s="0" outlineLevel="0">
+    <row r="158">
       <c r="A158" t="inlineStr">
         <is>
           <t>72037_4</t>
@@ -2281,7 +2324,7 @@
         </is>
       </c>
     </row>
-    <row r="159" spans="1:2" s="0" outlineLevel="0">
+    <row r="159">
       <c r="A159" t="inlineStr">
         <is>
           <t>72038_1</t>
@@ -2293,7 +2336,7 @@
         </is>
       </c>
     </row>
-    <row r="160" spans="1:2" s="0" outlineLevel="0">
+    <row r="160">
       <c r="A160" t="inlineStr">
         <is>
           <t>72038_2</t>
@@ -2305,7 +2348,7 @@
         </is>
       </c>
     </row>
-    <row r="161" spans="1:2" s="0" outlineLevel="0">
+    <row r="161">
       <c r="A161" t="inlineStr">
         <is>
           <t>72038_3</t>
@@ -2317,7 +2360,7 @@
         </is>
       </c>
     </row>
-    <row r="162" spans="1:2" s="0" outlineLevel="0">
+    <row r="162">
       <c r="A162" t="inlineStr">
         <is>
           <t>72039_1</t>
@@ -2329,7 +2372,7 @@
         </is>
       </c>
     </row>
-    <row r="163" spans="1:2" s="0" outlineLevel="0">
+    <row r="163">
       <c r="A163" t="inlineStr">
         <is>
           <t>72039_2</t>
@@ -2341,7 +2384,7 @@
         </is>
       </c>
     </row>
-    <row r="164" spans="1:2" s="0" outlineLevel="0">
+    <row r="164">
       <c r="A164" t="inlineStr">
         <is>
           <t>72039_3</t>
@@ -2353,7 +2396,7 @@
         </is>
       </c>
     </row>
-    <row r="165" spans="1:2" s="0" outlineLevel="0">
+    <row r="165">
       <c r="A165" t="inlineStr">
         <is>
           <t>72039_5</t>
@@ -2365,7 +2408,7 @@
         </is>
       </c>
     </row>
-    <row r="166" spans="1:2" s="0" outlineLevel="0">
+    <row r="166">
       <c r="A166" t="inlineStr">
         <is>
           <t>72039_6</t>
@@ -2377,7 +2420,7 @@
         </is>
       </c>
     </row>
-    <row r="167" spans="1:2" s="0" outlineLevel="0">
+    <row r="167">
       <c r="A167" t="inlineStr">
         <is>
           <t>72039_7</t>
@@ -2389,7 +2432,7 @@
         </is>
       </c>
     </row>
-    <row r="168" spans="1:2" s="0" outlineLevel="0">
+    <row r="168">
       <c r="A168" t="inlineStr">
         <is>
           <t>72041_1</t>
@@ -2401,7 +2444,7 @@
         </is>
       </c>
     </row>
-    <row r="169" spans="1:2" s="0" outlineLevel="0">
+    <row r="169">
       <c r="A169" t="inlineStr">
         <is>
           <t>72041_2</t>
@@ -2413,7 +2456,7 @@
         </is>
       </c>
     </row>
-    <row r="170" spans="1:2" s="0" outlineLevel="0">
+    <row r="170">
       <c r="A170" t="inlineStr">
         <is>
           <t>72041_3</t>
@@ -2425,7 +2468,7 @@
         </is>
       </c>
     </row>
-    <row r="171" spans="1:2" s="0" outlineLevel="0">
+    <row r="171">
       <c r="A171" t="inlineStr">
         <is>
           <t>72041_5</t>
@@ -2437,7 +2480,7 @@
         </is>
       </c>
     </row>
-    <row r="172" spans="1:2" s="0" outlineLevel="0">
+    <row r="172">
       <c r="A172" t="inlineStr">
         <is>
           <t>72041_6</t>
@@ -2449,7 +2492,7 @@
         </is>
       </c>
     </row>
-    <row r="173" spans="1:2" s="0" outlineLevel="0">
+    <row r="173">
       <c r="A173" t="inlineStr">
         <is>
           <t>72042_1</t>
@@ -2461,7 +2504,7 @@
         </is>
       </c>
     </row>
-    <row r="174" spans="1:2" s="0" outlineLevel="0">
+    <row r="174">
       <c r="A174" t="inlineStr">
         <is>
           <t>72042_2</t>
@@ -2473,7 +2516,7 @@
         </is>
       </c>
     </row>
-    <row r="175" spans="1:2" s="0" outlineLevel="0">
+    <row r="175">
       <c r="A175" t="inlineStr">
         <is>
           <t>72042_3</t>
@@ -2485,7 +2528,7 @@
         </is>
       </c>
     </row>
-    <row r="176" spans="1:2" s="0" outlineLevel="0">
+    <row r="176">
       <c r="A176" t="inlineStr">
         <is>
           <t>72042_4</t>
@@ -2497,7 +2540,7 @@
         </is>
       </c>
     </row>
-    <row r="177" spans="1:2" s="0" outlineLevel="0">
+    <row r="177">
       <c r="A177" t="inlineStr">
         <is>
           <t>72042_5</t>
@@ -2509,7 +2552,7 @@
         </is>
       </c>
     </row>
-    <row r="178" spans="1:2" s="0" outlineLevel="0">
+    <row r="178">
       <c r="A178" t="inlineStr">
         <is>
           <t>72042_6</t>
@@ -2521,7 +2564,7 @@
         </is>
       </c>
     </row>
-    <row r="179" spans="1:2" s="0" outlineLevel="0">
+    <row r="179">
       <c r="A179" t="inlineStr">
         <is>
           <t>72042_7</t>
@@ -2533,7 +2576,7 @@
         </is>
       </c>
     </row>
-    <row r="180" spans="1:2" s="0" outlineLevel="0">
+    <row r="180">
       <c r="A180" t="inlineStr">
         <is>
           <t>72042_8</t>
@@ -2545,7 +2588,7 @@
         </is>
       </c>
     </row>
-    <row r="181" spans="1:2" s="0" outlineLevel="0">
+    <row r="181">
       <c r="A181" t="inlineStr">
         <is>
           <t>72043_1</t>
@@ -2557,7 +2600,7 @@
         </is>
       </c>
     </row>
-    <row r="182" spans="1:2" s="0" outlineLevel="0">
+    <row r="182">
       <c r="A182" t="inlineStr">
         <is>
           <t>72043_2</t>
@@ -2569,7 +2612,7 @@
         </is>
       </c>
     </row>
-    <row r="183" spans="1:2" s="0" outlineLevel="0">
+    <row r="183">
       <c r="A183" t="inlineStr">
         <is>
           <t>72043_3</t>
@@ -2581,7 +2624,7 @@
         </is>
       </c>
     </row>
-    <row r="184" spans="1:2" s="0" outlineLevel="0">
+    <row r="184">
       <c r="A184" t="inlineStr">
         <is>
           <t>72043_4</t>
@@ -2593,7 +2636,7 @@
         </is>
       </c>
     </row>
-    <row r="185" spans="1:2" s="0" outlineLevel="0">
+    <row r="185">
       <c r="A185" t="inlineStr">
         <is>
           <t>72043_5</t>
@@ -2605,7 +2648,7 @@
         </is>
       </c>
     </row>
-    <row r="186" spans="1:2" s="0" outlineLevel="0">
+    <row r="186">
       <c r="A186" t="inlineStr">
         <is>
           <t>72043_6</t>
@@ -2617,7 +2660,7 @@
         </is>
       </c>
     </row>
-    <row r="187" spans="1:2" s="0" outlineLevel="0">
+    <row r="187">
       <c r="A187" t="inlineStr">
         <is>
           <t>72043_7</t>
@@ -2629,7 +2672,7 @@
         </is>
       </c>
     </row>
-    <row r="188" spans="1:2" s="0" outlineLevel="0">
+    <row r="188">
       <c r="A188" t="inlineStr">
         <is>
           <t>72043_8</t>
@@ -2641,7 +2684,7 @@
         </is>
       </c>
     </row>
-    <row r="189" spans="1:2" s="0" outlineLevel="0">
+    <row r="189">
       <c r="A189" t="inlineStr">
         <is>
           <t>72043_9</t>
@@ -2653,7 +2696,7 @@
         </is>
       </c>
     </row>
-    <row r="190" spans="1:2" s="0" outlineLevel="0">
+    <row r="190">
       <c r="A190" t="inlineStr">
         <is>
           <t>73001_1</t>
@@ -2665,7 +2708,7 @@
         </is>
       </c>
     </row>
-    <row r="191" spans="1:2" s="0" outlineLevel="0">
+    <row r="191">
       <c r="A191" t="inlineStr">
         <is>
           <t>73001_2</t>
@@ -2677,7 +2720,7 @@
         </is>
       </c>
     </row>
-    <row r="192" spans="1:2" s="0" outlineLevel="0">
+    <row r="192">
       <c r="A192" t="inlineStr">
         <is>
           <t>73001_3</t>
@@ -2689,7 +2732,7 @@
         </is>
       </c>
     </row>
-    <row r="193" spans="1:2" s="0" outlineLevel="0">
+    <row r="193">
       <c r="A193" t="inlineStr">
         <is>
           <t>73001_4</t>
@@ -2701,7 +2744,7 @@
         </is>
       </c>
     </row>
-    <row r="194" spans="1:2" s="0" outlineLevel="0">
+    <row r="194">
       <c r="A194" t="inlineStr">
         <is>
           <t>73006_1</t>
@@ -2713,7 +2756,7 @@
         </is>
       </c>
     </row>
-    <row r="195" spans="1:2" s="0" outlineLevel="0">
+    <row r="195">
       <c r="A195" t="inlineStr">
         <is>
           <t>73006_10</t>
@@ -2725,7 +2768,7 @@
         </is>
       </c>
     </row>
-    <row r="196" spans="1:2" s="0" outlineLevel="0">
+    <row r="196">
       <c r="A196" t="inlineStr">
         <is>
           <t>73006_11</t>
@@ -2737,7 +2780,7 @@
         </is>
       </c>
     </row>
-    <row r="197" spans="1:2" s="0" outlineLevel="0">
+    <row r="197">
       <c r="A197" t="inlineStr">
         <is>
           <t>73006_12</t>
@@ -2749,7 +2792,7 @@
         </is>
       </c>
     </row>
-    <row r="198" spans="1:2" s="0" outlineLevel="0">
+    <row r="198">
       <c r="A198" t="inlineStr">
         <is>
           <t>73006_13</t>
@@ -2761,7 +2804,7 @@
         </is>
       </c>
     </row>
-    <row r="199" spans="1:2" s="0" outlineLevel="0">
+    <row r="199">
       <c r="A199" t="inlineStr">
         <is>
           <t>73006_2</t>
@@ -2773,7 +2816,7 @@
         </is>
       </c>
     </row>
-    <row r="200" spans="1:2" s="0" outlineLevel="0">
+    <row r="200">
       <c r="A200" t="inlineStr">
         <is>
           <t>73006_3</t>
@@ -2785,7 +2828,7 @@
         </is>
       </c>
     </row>
-    <row r="201" spans="1:2" s="0" outlineLevel="0">
+    <row r="201">
       <c r="A201" t="inlineStr">
         <is>
           <t>73006_4</t>
@@ -2797,7 +2840,7 @@
         </is>
       </c>
     </row>
-    <row r="202" spans="1:2" s="0" outlineLevel="0">
+    <row r="202">
       <c r="A202" t="inlineStr">
         <is>
           <t>73006_5</t>
@@ -2809,7 +2852,7 @@
         </is>
       </c>
     </row>
-    <row r="203" spans="1:2" s="0" outlineLevel="0">
+    <row r="203">
       <c r="A203" t="inlineStr">
         <is>
           <t>73006_6</t>
@@ -2821,7 +2864,7 @@
         </is>
       </c>
     </row>
-    <row r="204" spans="1:2" s="0" outlineLevel="0">
+    <row r="204">
       <c r="A204" t="inlineStr">
         <is>
           <t>73006_7</t>
@@ -2833,7 +2876,7 @@
         </is>
       </c>
     </row>
-    <row r="205" spans="1:2" s="0" outlineLevel="0">
+    <row r="205">
       <c r="A205" t="inlineStr">
         <is>
           <t>73006_8</t>
@@ -2845,7 +2888,7 @@
         </is>
       </c>
     </row>
-    <row r="206" spans="1:2" s="0" outlineLevel="0">
+    <row r="206">
       <c r="A206" t="inlineStr">
         <is>
           <t>73006_9</t>
@@ -2857,7 +2900,7 @@
         </is>
       </c>
     </row>
-    <row r="207" spans="1:2" s="0" outlineLevel="0">
+    <row r="207">
       <c r="A207" t="inlineStr">
         <is>
           <t>73009_1</t>
@@ -2869,7 +2912,7 @@
         </is>
       </c>
     </row>
-    <row r="208" spans="1:2" s="0" outlineLevel="0">
+    <row r="208">
       <c r="A208" t="inlineStr">
         <is>
           <t>73009_2</t>
@@ -2881,7 +2924,7 @@
         </is>
       </c>
     </row>
-    <row r="209" spans="1:2" s="0" outlineLevel="0">
+    <row r="209">
       <c r="A209" t="inlineStr">
         <is>
           <t>73009_3</t>
@@ -2893,7 +2936,7 @@
         </is>
       </c>
     </row>
-    <row r="210" spans="1:2" s="0" outlineLevel="0">
+    <row r="210">
       <c r="A210" t="inlineStr">
         <is>
           <t>73009_4</t>
@@ -2905,7 +2948,7 @@
         </is>
       </c>
     </row>
-    <row r="211" spans="1:2" s="0" outlineLevel="0">
+    <row r="211">
       <c r="A211" t="inlineStr">
         <is>
           <t>73009_5</t>
@@ -2917,7 +2960,7 @@
         </is>
       </c>
     </row>
-    <row r="212" spans="1:2" s="0" outlineLevel="0">
+    <row r="212">
       <c r="A212" t="inlineStr">
         <is>
           <t>73009_6</t>
@@ -2929,7 +2972,7 @@
         </is>
       </c>
     </row>
-    <row r="213" spans="1:2" s="0" outlineLevel="0">
+    <row r="213">
       <c r="A213" t="inlineStr">
         <is>
           <t>73009_7</t>
@@ -2941,7 +2984,7 @@
         </is>
       </c>
     </row>
-    <row r="214" spans="1:2" s="0" outlineLevel="0">
+    <row r="214">
       <c r="A214" t="inlineStr">
         <is>
           <t>73009_8</t>
@@ -2953,7 +2996,7 @@
         </is>
       </c>
     </row>
-    <row r="215" spans="1:2" s="0" outlineLevel="0">
+    <row r="215">
       <c r="A215" t="inlineStr">
         <is>
           <t>73022_1</t>
@@ -2965,7 +3008,7 @@
         </is>
       </c>
     </row>
-    <row r="216" spans="1:2" s="0" outlineLevel="0">
+    <row r="216">
       <c r="A216" t="inlineStr">
         <is>
           <t>73022_2</t>
@@ -2977,7 +3020,7 @@
         </is>
       </c>
     </row>
-    <row r="217" spans="1:2" s="0" outlineLevel="0">
+    <row r="217">
       <c r="A217" t="inlineStr">
         <is>
           <t>73022_3</t>
@@ -2989,7 +3032,7 @@
         </is>
       </c>
     </row>
-    <row r="218" spans="1:2" s="0" outlineLevel="0">
+    <row r="218">
       <c r="A218" t="inlineStr">
         <is>
           <t>73022_4</t>
@@ -3001,7 +3044,7 @@
         </is>
       </c>
     </row>
-    <row r="219" spans="1:2" s="0" outlineLevel="0">
+    <row r="219">
       <c r="A219" t="inlineStr">
         <is>
           <t>73022_5</t>
@@ -3013,7 +3056,7 @@
         </is>
       </c>
     </row>
-    <row r="220" spans="1:2" s="0" outlineLevel="0">
+    <row r="220">
       <c r="A220" t="inlineStr">
         <is>
           <t>73022_6</t>
@@ -3025,7 +3068,7 @@
         </is>
       </c>
     </row>
-    <row r="221" spans="1:2" s="0" outlineLevel="0">
+    <row r="221">
       <c r="A221" t="inlineStr">
         <is>
           <t>73022_7</t>
@@ -3037,7 +3080,7 @@
         </is>
       </c>
     </row>
-    <row r="222" spans="1:2" s="0" outlineLevel="0">
+    <row r="222">
       <c r="A222" t="inlineStr">
         <is>
           <t>73028_1</t>
@@ -3049,7 +3092,7 @@
         </is>
       </c>
     </row>
-    <row r="223" spans="1:2" s="0" outlineLevel="0">
+    <row r="223">
       <c r="A223" t="inlineStr">
         <is>
           <t>73032_1</t>
@@ -3061,7 +3104,7 @@
         </is>
       </c>
     </row>
-    <row r="224" spans="1:2" s="0" outlineLevel="0">
+    <row r="224">
       <c r="A224" t="inlineStr">
         <is>
           <t>73032_2</t>
@@ -3073,7 +3116,7 @@
         </is>
       </c>
     </row>
-    <row r="225" spans="1:2" s="0" outlineLevel="0">
+    <row r="225">
       <c r="A225" t="inlineStr">
         <is>
           <t>73032_3</t>
@@ -3085,7 +3128,7 @@
         </is>
       </c>
     </row>
-    <row r="226" spans="1:2" s="0" outlineLevel="0">
+    <row r="226">
       <c r="A226" t="inlineStr">
         <is>
           <t>73032_4</t>
@@ -3097,7 +3140,7 @@
         </is>
       </c>
     </row>
-    <row r="227" spans="1:2" s="0" outlineLevel="0">
+    <row r="227">
       <c r="A227" t="inlineStr">
         <is>
           <t>73032_5</t>
@@ -3109,7 +3152,7 @@
         </is>
       </c>
     </row>
-    <row r="228" spans="1:2" s="0" outlineLevel="0">
+    <row r="228">
       <c r="A228" t="inlineStr">
         <is>
           <t>73032_6</t>
@@ -3121,7 +3164,7 @@
         </is>
       </c>
     </row>
-    <row r="229" spans="1:2" s="0" outlineLevel="0">
+    <row r="229">
       <c r="A229" t="inlineStr">
         <is>
           <t>73032_7</t>
@@ -3133,7 +3176,7 @@
         </is>
       </c>
     </row>
-    <row r="230" spans="1:2" s="0" outlineLevel="0">
+    <row r="230">
       <c r="A230" t="inlineStr">
         <is>
           <t>73040_1</t>
@@ -3145,7 +3188,7 @@
         </is>
       </c>
     </row>
-    <row r="231" spans="1:2" s="0" outlineLevel="0">
+    <row r="231">
       <c r="A231" t="inlineStr">
         <is>
           <t>73040_2</t>
@@ -3157,7 +3200,7 @@
         </is>
       </c>
     </row>
-    <row r="232" spans="1:2" s="0" outlineLevel="0">
+    <row r="232">
       <c r="A232" t="inlineStr">
         <is>
           <t>73040_3</t>
@@ -3169,7 +3212,7 @@
         </is>
       </c>
     </row>
-    <row r="233" spans="1:2" s="0" outlineLevel="0">
+    <row r="233">
       <c r="A233" t="inlineStr">
         <is>
           <t>73040_4</t>
@@ -3181,7 +3224,7 @@
         </is>
       </c>
     </row>
-    <row r="234" spans="1:2" s="0" outlineLevel="0">
+    <row r="234">
       <c r="A234" t="inlineStr">
         <is>
           <t>73040_5</t>
@@ -3193,7 +3236,7 @@
         </is>
       </c>
     </row>
-    <row r="235" spans="1:2" s="0" outlineLevel="0">
+    <row r="235">
       <c r="A235" t="inlineStr">
         <is>
           <t>73042_1</t>
@@ -3205,7 +3248,7 @@
         </is>
       </c>
     </row>
-    <row r="236" spans="1:2" s="0" outlineLevel="0">
+    <row r="236">
       <c r="A236" t="inlineStr">
         <is>
           <t>73042_2</t>
@@ -3217,7 +3260,7 @@
         </is>
       </c>
     </row>
-    <row r="237" spans="1:2" s="0" outlineLevel="0">
+    <row r="237">
       <c r="A237" t="inlineStr">
         <is>
           <t>73042_3</t>
@@ -3229,7 +3272,7 @@
         </is>
       </c>
     </row>
-    <row r="238" spans="1:2" s="0" outlineLevel="0">
+    <row r="238">
       <c r="A238" t="inlineStr">
         <is>
           <t>73042_4</t>
@@ -3241,7 +3284,7 @@
         </is>
       </c>
     </row>
-    <row r="239" spans="1:2" s="0" outlineLevel="0">
+    <row r="239">
       <c r="A239" t="inlineStr">
         <is>
           <t>73042_5</t>
@@ -3253,7 +3296,7 @@
         </is>
       </c>
     </row>
-    <row r="240" spans="1:2" s="0" outlineLevel="0">
+    <row r="240">
       <c r="A240" t="inlineStr">
         <is>
           <t>73042_6</t>
@@ -3265,7 +3308,7 @@
         </is>
       </c>
     </row>
-    <row r="241" spans="1:2" s="0" outlineLevel="0">
+    <row r="241">
       <c r="A241" t="inlineStr">
         <is>
           <t>73042_7</t>
@@ -3277,7 +3320,7 @@
         </is>
       </c>
     </row>
-    <row r="242" spans="1:2" s="0" outlineLevel="0">
+    <row r="242">
       <c r="A242" t="inlineStr">
         <is>
           <t>73066_1</t>
@@ -3289,7 +3332,7 @@
         </is>
       </c>
     </row>
-    <row r="243" spans="1:2" s="0" outlineLevel="0">
+    <row r="243">
       <c r="A243" t="inlineStr">
         <is>
           <t>73066_10</t>
@@ -3301,7 +3344,7 @@
         </is>
       </c>
     </row>
-    <row r="244" spans="1:2" s="0" outlineLevel="0">
+    <row r="244">
       <c r="A244" t="inlineStr">
         <is>
           <t>73066_11</t>
@@ -3313,7 +3356,7 @@
         </is>
       </c>
     </row>
-    <row r="245" spans="1:2" s="0" outlineLevel="0">
+    <row r="245">
       <c r="A245" t="inlineStr">
         <is>
           <t>73066_12</t>
@@ -3325,7 +3368,7 @@
         </is>
       </c>
     </row>
-    <row r="246" spans="1:2" s="0" outlineLevel="0">
+    <row r="246">
       <c r="A246" t="inlineStr">
         <is>
           <t>73066_2</t>
@@ -3337,7 +3380,7 @@
         </is>
       </c>
     </row>
-    <row r="247" spans="1:2" s="0" outlineLevel="0">
+    <row r="247">
       <c r="A247" t="inlineStr">
         <is>
           <t>73066_3</t>
@@ -3349,7 +3392,7 @@
         </is>
       </c>
     </row>
-    <row r="248" spans="1:2" s="0" outlineLevel="0">
+    <row r="248">
       <c r="A248" t="inlineStr">
         <is>
           <t>73066_4</t>
@@ -3361,7 +3404,7 @@
         </is>
       </c>
     </row>
-    <row r="249" spans="1:2" s="0" outlineLevel="0">
+    <row r="249">
       <c r="A249" t="inlineStr">
         <is>
           <t>73066_5</t>
@@ -3373,7 +3416,7 @@
         </is>
       </c>
     </row>
-    <row r="250" spans="1:2" s="0" outlineLevel="0">
+    <row r="250">
       <c r="A250" t="inlineStr">
         <is>
           <t>73066_6</t>
@@ -3385,7 +3428,7 @@
         </is>
       </c>
     </row>
-    <row r="251" spans="1:2" s="0" outlineLevel="0">
+    <row r="251">
       <c r="A251" t="inlineStr">
         <is>
           <t>73066_7</t>
@@ -3397,7 +3440,7 @@
         </is>
       </c>
     </row>
-    <row r="252" spans="1:2" s="0" outlineLevel="0">
+    <row r="252">
       <c r="A252" t="inlineStr">
         <is>
           <t>73066_8</t>
@@ -3409,7 +3452,7 @@
         </is>
       </c>
     </row>
-    <row r="253" spans="1:2" s="0" outlineLevel="0">
+    <row r="253">
       <c r="A253" t="inlineStr">
         <is>
           <t>73066_9</t>
@@ -3421,7 +3464,7 @@
         </is>
       </c>
     </row>
-    <row r="254" spans="1:2" s="0" outlineLevel="0">
+    <row r="254">
       <c r="A254" t="inlineStr">
         <is>
           <t>73083_1</t>
@@ -3433,7 +3476,7 @@
         </is>
       </c>
     </row>
-    <row r="255" spans="1:2" s="0" outlineLevel="0">
+    <row r="255">
       <c r="A255" t="inlineStr">
         <is>
           <t>73083_10</t>
@@ -3445,7 +3488,7 @@
         </is>
       </c>
     </row>
-    <row r="256" spans="1:2" s="0" outlineLevel="0">
+    <row r="256">
       <c r="A256" t="inlineStr">
         <is>
           <t>73083_11</t>
@@ -3457,7 +3500,7 @@
         </is>
       </c>
     </row>
-    <row r="257" spans="1:2" s="0" outlineLevel="0">
+    <row r="257">
       <c r="A257" t="inlineStr">
         <is>
           <t>73083_12</t>
@@ -3469,7 +3512,7 @@
         </is>
       </c>
     </row>
-    <row r="258" spans="1:2" s="0" outlineLevel="0">
+    <row r="258">
       <c r="A258" t="inlineStr">
         <is>
           <t>73083_13</t>
@@ -3481,7 +3524,7 @@
         </is>
       </c>
     </row>
-    <row r="259" spans="1:2" s="0" outlineLevel="0">
+    <row r="259">
       <c r="A259" t="inlineStr">
         <is>
           <t>73083_14</t>
@@ -3493,7 +3536,7 @@
         </is>
       </c>
     </row>
-    <row r="260" spans="1:2" s="0" outlineLevel="0">
+    <row r="260">
       <c r="A260" t="inlineStr">
         <is>
           <t>73083_15</t>
@@ -3505,7 +3548,7 @@
         </is>
       </c>
     </row>
-    <row r="261" spans="1:2" s="0" outlineLevel="0">
+    <row r="261">
       <c r="A261" t="inlineStr">
         <is>
           <t>73083_2</t>
@@ -3517,7 +3560,7 @@
         </is>
       </c>
     </row>
-    <row r="262" spans="1:2" s="0" outlineLevel="0">
+    <row r="262">
       <c r="A262" t="inlineStr">
         <is>
           <t>73083_3</t>
@@ -3529,7 +3572,7 @@
         </is>
       </c>
     </row>
-    <row r="263" spans="1:2" s="0" outlineLevel="0">
+    <row r="263">
       <c r="A263" t="inlineStr">
         <is>
           <t>73083_4</t>
@@ -3541,7 +3584,7 @@
         </is>
       </c>
     </row>
-    <row r="264" spans="1:2" s="0" outlineLevel="0">
+    <row r="264">
       <c r="A264" t="inlineStr">
         <is>
           <t>73083_5</t>
@@ -3553,7 +3596,7 @@
         </is>
       </c>
     </row>
-    <row r="265" spans="1:2" s="0" outlineLevel="0">
+    <row r="265">
       <c r="A265" t="inlineStr">
         <is>
           <t>73083_6</t>
@@ -3565,7 +3608,7 @@
         </is>
       </c>
     </row>
-    <row r="266" spans="1:2" s="0" outlineLevel="0">
+    <row r="266">
       <c r="A266" t="inlineStr">
         <is>
           <t>73083_7</t>
@@ -3577,7 +3620,7 @@
         </is>
       </c>
     </row>
-    <row r="267" spans="1:2" s="0" outlineLevel="0">
+    <row r="267">
       <c r="A267" t="inlineStr">
         <is>
           <t>73083_8</t>
@@ -3589,7 +3632,7 @@
         </is>
       </c>
     </row>
-    <row r="268" spans="1:2" s="0" outlineLevel="0">
+    <row r="268">
       <c r="A268" t="inlineStr">
         <is>
           <t>73083_9</t>
@@ -3601,7 +3644,7 @@
         </is>
       </c>
     </row>
-    <row r="269" spans="1:2" s="0" outlineLevel="0">
+    <row r="269">
       <c r="A269" t="inlineStr">
         <is>
           <t>73098_1</t>
@@ -3613,7 +3656,7 @@
         </is>
       </c>
     </row>
-    <row r="270" spans="1:2" s="0" outlineLevel="0">
+    <row r="270">
       <c r="A270" t="inlineStr">
         <is>
           <t>73098_2</t>
@@ -3625,7 +3668,7 @@
         </is>
       </c>
     </row>
-    <row r="271" spans="1:2" s="0" outlineLevel="0">
+    <row r="271">
       <c r="A271" t="inlineStr">
         <is>
           <t>73098_3</t>
@@ -3637,7 +3680,7 @@
         </is>
       </c>
     </row>
-    <row r="272" spans="1:2" s="0" outlineLevel="0">
+    <row r="272">
       <c r="A272" t="inlineStr">
         <is>
           <t>73107_1</t>
@@ -3649,7 +3692,7 @@
         </is>
       </c>
     </row>
-    <row r="273" spans="1:2" s="0" outlineLevel="0">
+    <row r="273">
       <c r="A273" t="inlineStr">
         <is>
           <t>73107_10</t>
@@ -3661,7 +3704,7 @@
         </is>
       </c>
     </row>
-    <row r="274" spans="1:2" s="0" outlineLevel="0">
+    <row r="274">
       <c r="A274" t="inlineStr">
         <is>
           <t>73107_2</t>
@@ -3673,7 +3716,7 @@
         </is>
       </c>
     </row>
-    <row r="275" spans="1:2" s="0" outlineLevel="0">
+    <row r="275">
       <c r="A275" t="inlineStr">
         <is>
           <t>73107_3</t>
@@ -3685,7 +3728,7 @@
         </is>
       </c>
     </row>
-    <row r="276" spans="1:2" s="0" outlineLevel="0">
+    <row r="276">
       <c r="A276" t="inlineStr">
         <is>
           <t>73107_4</t>
@@ -3697,7 +3740,7 @@
         </is>
       </c>
     </row>
-    <row r="277" spans="1:2" s="0" outlineLevel="0">
+    <row r="277">
       <c r="A277" t="inlineStr">
         <is>
           <t>73107_5</t>
@@ -3709,7 +3752,7 @@
         </is>
       </c>
     </row>
-    <row r="278" spans="1:2" s="0" outlineLevel="0">
+    <row r="278">
       <c r="A278" t="inlineStr">
         <is>
           <t>73107_6</t>
@@ -3721,7 +3764,7 @@
         </is>
       </c>
     </row>
-    <row r="279" spans="1:2" s="0" outlineLevel="0">
+    <row r="279">
       <c r="A279" t="inlineStr">
         <is>
           <t>73107_7</t>
@@ -3733,7 +3776,7 @@
         </is>
       </c>
     </row>
-    <row r="280" spans="1:2" s="0" outlineLevel="0">
+    <row r="280">
       <c r="A280" t="inlineStr">
         <is>
           <t>73107_8</t>
@@ -3745,7 +3788,7 @@
         </is>
       </c>
     </row>
-    <row r="281" spans="1:2" s="0" outlineLevel="0">
+    <row r="281">
       <c r="A281" t="inlineStr">
         <is>
           <t>73107_9</t>
@@ -3757,7 +3800,7 @@
         </is>
       </c>
     </row>
-    <row r="282" spans="1:2" s="0" outlineLevel="0">
+    <row r="282">
       <c r="A282" t="inlineStr">
         <is>
           <t>73109_1</t>
@@ -3769,7 +3812,7 @@
         </is>
       </c>
     </row>
-    <row r="283" spans="1:2" s="0" outlineLevel="0">
+    <row r="283">
       <c r="A283" t="inlineStr">
         <is>
           <t>73109_2</t>
@@ -3781,7 +3824,7 @@
         </is>
       </c>
     </row>
-    <row r="284" spans="1:2" s="0" outlineLevel="0">
+    <row r="284">
       <c r="A284" t="inlineStr">
         <is>
           <t>73109_3</t>
@@ -3793,7 +3836,7 @@
         </is>
       </c>
     </row>
-    <row r="285" spans="1:2" s="0" outlineLevel="0">
+    <row r="285">
       <c r="A285" t="inlineStr">
         <is>
           <t>73109_4</t>
@@ -3805,7 +3848,7 @@
         </is>
       </c>
     </row>
-    <row r="286" spans="1:2" s="0" outlineLevel="0">
+    <row r="286">
       <c r="A286" t="inlineStr">
         <is>
           <t>RWM_MLO_BG</t>
@@ -3817,7 +3860,7 @@
         </is>
       </c>
     </row>
-    <row r="287" spans="1:2" s="0" outlineLevel="0">
+    <row r="287">
       <c r="A287" t="inlineStr">
         <is>
           <t>RWM_MLW_BG</t>
@@ -3829,7 +3872,7 @@
         </is>
       </c>
     </row>
-    <row r="288" spans="1:2" s="0" outlineLevel="0">
+    <row r="288">
       <c r="A288" t="inlineStr">
         <is>
           <t>RWM_NL_BG</t>
@@ -3841,7 +3884,7 @@
         </is>
       </c>
     </row>
-    <row r="289" spans="1:2" s="0" outlineLevel="0">
+    <row r="289">
       <c r="A289" t="inlineStr">
         <is>
           <t>RWM_NL_RE</t>
@@ -3853,7 +3896,7 @@
         </is>
       </c>
     </row>
-    <row r="290" spans="1:2" s="0" outlineLevel="0">
+    <row r="290">
       <c r="A290" t="inlineStr">
         <is>
           <t>RWM_NOL_BG</t>
@@ -3865,7 +3908,7 @@
         </is>
       </c>
     </row>
-    <row r="291" spans="1:2" s="0" outlineLevel="0">
+    <row r="291">
       <c r="A291" t="inlineStr">
         <is>
           <t>RWM_NWL_BG</t>
@@ -3877,7 +3920,7 @@
         </is>
       </c>
     </row>
-    <row r="292" spans="1:2" s="0" outlineLevel="0">
+    <row r="292">
       <c r="A292" t="inlineStr">
         <is>
           <t>RWM_OL_BG</t>
@@ -3889,7 +3932,7 @@
         </is>
       </c>
     </row>
-    <row r="293" spans="1:2" s="0" outlineLevel="0">
+    <row r="293">
       <c r="A293" t="inlineStr">
         <is>
           <t>RWM_V_BG</t>
@@ -3901,7 +3944,7 @@
         </is>
       </c>
     </row>
-    <row r="294" spans="1:2" s="0" outlineLevel="0">
+    <row r="294">
       <c r="A294" t="inlineStr">
         <is>
           <t>RWM_WL_BG</t>
@@ -3913,7 +3956,7 @@
         </is>
       </c>
     </row>
-    <row r="295" spans="1:2" s="0" outlineLevel="0">
+    <row r="295">
       <c r="A295" t="inlineStr">
         <is>
           <t>RWM_ZOL_BG</t>
@@ -3925,7 +3968,7 @@
         </is>
       </c>
     </row>
-    <row r="296" spans="1:2" s="0" outlineLevel="0">
+    <row r="296">
       <c r="A296" t="inlineStr">
         <is>
           <t>RWM_ZWL_BG</t>
@@ -3938,6 +3981,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>